--- a/history/loss_history.xlsx
+++ b/history/loss_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:T211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,46 @@
           <t>norm_bio_2</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>gang_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>hoon_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>gang_2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>hoon_2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>norm_gang_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>norm_hoon_1</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>norm_gang_1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>norm_hoon_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -515,6 +555,30 @@
       <c r="L2" t="n">
         <v>0.05022702813148498</v>
       </c>
+      <c r="M2" t="n">
+        <v>3.423077344894409</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1425601243972778</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.514613151550293</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1153851300477982</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>14.66986274719238</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1028797253966331</v>
+      </c>
+      <c r="S2" t="n">
+        <v>18.52042198181152</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.270382404327393</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -553,6 +617,30 @@
       <c r="L3" t="n">
         <v>0.3316045880317688</v>
       </c>
+      <c r="M3" t="n">
+        <v>2.226003885269165</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2264468669891357</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4031641781330109</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1229772940278053</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>14.33411502838135</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03039708361029625</v>
+      </c>
+      <c r="S3" t="n">
+        <v>17.38631629943848</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.694362163543701</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -591,6 +679,30 @@
       <c r="L4" t="n">
         <v>0.1567508347332477</v>
       </c>
+      <c r="M4" t="n">
+        <v>1.191092252731323</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1991186141967773</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3595923781394958</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.09915038198232651</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>16.5833568572998</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9896373152732849</v>
+      </c>
+      <c r="S4" t="n">
+        <v>19.017578125</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.842783451080322</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -629,6 +741,30 @@
       <c r="L5" t="n">
         <v>0.3727630108594894</v>
       </c>
+      <c r="M5" t="n">
+        <v>0.29225754737854</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1212424710392952</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4553126096725464</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1000268012285233</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.49824142456055</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.008048807270824909</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15.47902393341064</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.79844331741333</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -667,6 +803,30 @@
       <c r="L6" t="n">
         <v>0.4282803118228912</v>
       </c>
+      <c r="M6" t="n">
+        <v>0.3186963796615601</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3698894679546356</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3195627927780151</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.09636970609426498</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15.35581493377686</v>
+      </c>
+      <c r="R6" t="n">
+        <v/>
+      </c>
+      <c r="S6" t="n">
+        <v>12.90096092224121</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.416139841079712</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -705,6 +865,30 @@
       <c r="L7" t="n">
         <v>0.1966020906111225</v>
       </c>
+      <c r="M7" t="n">
+        <v>0.4490782618522644</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1527355313301086</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4315459132194519</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1187151297926903</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.46135997772217</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.507471561431885</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12.81864643096924</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.063985705375671</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -743,6 +927,30 @@
       <c r="L8" t="n">
         <v>0.1458103328943253</v>
       </c>
+      <c r="M8" t="n">
+        <v>0.2443496733903885</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2686876952648163</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2537178993225098</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1159055382013321</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15.59962463378906</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.04799546301364899</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11.69263648986816</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.575632810592651</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -781,6 +989,30 @@
       <c r="L9" t="n">
         <v>0.2972659289836884</v>
       </c>
+      <c r="M9" t="n">
+        <v>0.6867229342460632</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2366236746311188</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3309618234634399</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1123873293399811</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.594559192657471</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.03132068738341331</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12.31965065002441</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.827066659927368</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -819,6 +1051,30 @@
       <c r="L10" t="n">
         <v>0.1152410283684731</v>
       </c>
+      <c r="M10" t="n">
+        <v>0.294420063495636</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2226865440607071</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2550998330116272</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1007627099752426</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.684030055999756</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.556658387184143</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7.298967361450195</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.016472339630127</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -857,6 +1113,30 @@
       <c r="L11" t="n">
         <v>0.1404002122581005</v>
       </c>
+      <c r="M11" t="n">
+        <v>0.2530042827129364</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1233295574784279</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3383238315582275</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.09732640534639359</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.279011011123657</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.435723543167114</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7.903822898864746</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.808943271636963</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -895,6 +1175,30 @@
       <c r="L12" t="n">
         <v>0.2363098472356796</v>
       </c>
+      <c r="M12" t="n">
+        <v>0.3360653817653656</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.004179590847343206</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1941254436969757</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1290591955184937</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>13.17301177978516</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7548579573631287</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8.570270538330078</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.582381963729858</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -933,6 +1237,30 @@
       <c r="L13" t="n">
         <v>0.566354738920927</v>
       </c>
+      <c r="M13" t="n">
+        <v>1.029767632484436</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1976616084575653</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2368841022253036</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1037386506795883</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>14.02129650115967</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.05072947591543198</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.526040554046631</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.314045429229736</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -971,6 +1299,30 @@
       <c r="L14" t="n">
         <v>0.06765334364026784</v>
       </c>
+      <c r="M14" t="n">
+        <v>0.1987935602664948</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.005091921892017126</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.219411626458168</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1109188348054886</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>14.13692474365234</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.002855435945093632</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9.31641960144043</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.493326902389526</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1009,6 +1361,30 @@
       <c r="L15" t="n">
         <v>0.05396819743327796</v>
       </c>
+      <c r="M15" t="n">
+        <v>0.6022315621376038</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.119542583823204</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.2194179892539978</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1339498907327652</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9.568865776062012</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.219478726387024</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.814191341400146</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.884795069694519</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1047,6 +1423,30 @@
       <c r="L16" t="n">
         <v>0.3947577774524689</v>
       </c>
+      <c r="M16" t="n">
+        <v>0.918081521987915</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1788928210735321</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1929978728294373</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1172403767704964</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10.3586483001709</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.005376128479838371</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.261816501617432</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.649102807044983</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1085,6 +1485,30 @@
       <c r="L17" t="n">
         <v>0.109168516099453</v>
       </c>
+      <c r="M17" t="n">
+        <v>0.2490028291940689</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1179623901844025</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.234277218580246</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1106406524777412</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.5878586769104</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.488667011260986</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.960039138793945</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.671609878540039</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1123,6 +1547,30 @@
       <c r="L18" t="n">
         <v>0.2629106044769287</v>
       </c>
+      <c r="M18" t="n">
+        <v>0.291979193687439</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1482139974832535</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1811150014400482</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1317789405584335</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.87942361831665</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.09039749205112457</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.986457347869873</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.509044766426086</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1161,6 +1609,30 @@
       <c r="L19" t="n">
         <v>0.277634134888649</v>
       </c>
+      <c r="M19" t="n">
+        <v>0.1726893037557602</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1341058760881424</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.1805536895990372</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1007665693759918</v>
+      </c>
+      <c r="Q19" t="n">
+        <v/>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0007008241955190897</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6.502165794372559</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.1550211608409882</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1199,6 +1671,30 @@
       <c r="L20" t="n">
         <v>0.05421513437759131</v>
       </c>
+      <c r="M20" t="n">
+        <v>0.4872503280639648</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1751767992973328</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.2222642153501511</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1381862908601761</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8.643444061279297</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3536880910396576</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.631576538085938</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.9094387292861938</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1237,6 +1733,30 @@
       <c r="L21" t="n">
         <v>0.2205934315919876</v>
       </c>
+      <c r="M21" t="n">
+        <v>0.9057002067565918</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.235313281416893</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2230679094791412</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1201248019933701</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.738900184631348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.8327125310897827</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6.893101215362549</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.362256169319153</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1275,6 +1795,30 @@
       <c r="L22" t="n">
         <v>0.2665030106902123</v>
       </c>
+      <c r="M22" t="n">
+        <v>0.4575051367282867</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.1692163050174713</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.1475726962089539</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.09473061561584473</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.026401042938232</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.0148825328797102</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7.79926872253418</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.381940841674805</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1313,6 +1857,30 @@
       <c r="L23" t="n">
         <v>0.03062596283853054</v>
       </c>
+      <c r="M23" t="n">
+        <v>0.2370310127735138</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.342387318611145</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1933390200138092</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.09039326012134552</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.006981500890105963</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1532734483480453</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.26753568649292</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.021586537361145</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1351,6 +1919,30 @@
       <c r="L24" t="n">
         <v>0.4686899870634079</v>
       </c>
+      <c r="M24" t="n">
+        <v>0.6015868186950684</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.183618038892746</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1620411276817322</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1012538745999336</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.688001155853271</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4194939136505127</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.356412887573242</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.266334414482117</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1389,6 +1981,30 @@
       <c r="L25" t="n">
         <v>0.1727139821276069</v>
       </c>
+      <c r="M25" t="n">
+        <v>0.2222228944301605</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2652763724327087</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1422644257545471</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.09602703899145126</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5.754739284515381</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.01915241219103336</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.609754085540771</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.441841840744019</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1427,6 +2043,30 @@
       <c r="L26" t="n">
         <v>0.1476970858871937</v>
       </c>
+      <c r="M26" t="n">
+        <v>0.4859666526317596</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.2150809764862061</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1380591094493866</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1106294617056847</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.748066902160645</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1811245232820511</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.013625144958496</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.111102819442749</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1465,6 +2105,30 @@
       <c r="L27" t="n">
         <v>0.1398253381252289</v>
       </c>
+      <c r="M27" t="n">
+        <v>0.2469958961009979</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.2226805090904236</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.1435895264148712</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.09068498015403748</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.7488359808921814</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.680516123771667</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.073825359344482</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.66575038433075</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1503,6 +2167,30 @@
       <c r="L28" t="n">
         <v>0.2393288039602339</v>
       </c>
+      <c r="M28" t="n">
+        <v>0.3041291236877441</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.1903539896011353</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1390359699726105</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.09613732993602753</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.05348539352417</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.797136187553406</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6.091484546661377</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6.319657802581787</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1541,6 +2229,30 @@
       <c r="L29" t="n">
         <v>0.146305325627327</v>
       </c>
+      <c r="M29" t="n">
+        <v>0.3390510976314545</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.1800376772880554</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.1386651992797852</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.1035924628376961</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.568882703781128</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3511449992656708</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7.739113330841064</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.697862982749939</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1579,6 +2291,30 @@
       <c r="L30" t="n">
         <v>0.4061115093529225</v>
       </c>
+      <c r="M30" t="n">
+        <v>0.2960534691810608</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.1610250025987625</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.1700805276632309</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.09471295773983002</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.018255949020386</v>
+      </c>
+      <c r="R30" t="n">
+        <v/>
+      </c>
+      <c r="S30" t="n">
+        <v>5.046872138977051</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.349924564361572</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1617,6 +2353,30 @@
       <c r="L31" t="n">
         <v>0.3664370059967041</v>
       </c>
+      <c r="M31" t="n">
+        <v>0.5005679130554199</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.2395363003015518</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.1504094749689102</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.1217729672789574</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.917259931564331</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.002342696534469724</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.593790531158447</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.6153472661972046</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1655,6 +2415,30 @@
       <c r="L32" t="n">
         <v>0.06805221140384674</v>
       </c>
+      <c r="M32" t="n">
+        <v>0.4051131010055542</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.1639663279056549</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.1603893339633942</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.1011951565742493</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.1687541604042053</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.926853537559509</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.382875442504883</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.966272950172424</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1693,6 +2477,30 @@
       <c r="L33" t="n">
         <v>0.4352211348712444</v>
       </c>
+      <c r="M33" t="n">
+        <v>0.3420200943946838</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.1146244630217552</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.1315877735614777</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.09636297076940536</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.044480800628662</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.04385331645607948</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.30291748046875</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.347805857658386</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1731,6 +2539,30 @@
       <c r="L34" t="n">
         <v>0.2378279358148575</v>
       </c>
+      <c r="M34" t="n">
+        <v>0.3513720035552979</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.1922776103019714</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.1589739173650742</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.1097037494182587</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.424606084823608</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.162090003490448</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.479759454727173</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.773229241371155</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1769,6 +2601,30 @@
       <c r="L35" t="n">
         <v>0.3666657507419586</v>
       </c>
+      <c r="M35" t="n">
+        <v>0.2606260776519775</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.2179830521345139</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.1381880640983582</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.1176434680819511</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.8157254457473755</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.006044771987944841</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6.502012729644775</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.044428825378418</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1807,6 +2663,30 @@
       <c r="L36" t="n">
         <v>0.1401228412985802</v>
       </c>
+      <c r="M36" t="n">
+        <v>0.2984461486339569</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.2799165844917297</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1578358560800552</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.1031071692705154</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.2151418924331665</v>
+      </c>
+      <c r="R36" t="n">
+        <v/>
+      </c>
+      <c r="S36" t="n">
+        <v>2.790562152862549</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.8046119213104248</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1845,6 +2725,30 @@
       <c r="L37" t="n">
         <v>0.08601424023509026</v>
       </c>
+      <c r="M37" t="n">
+        <v>0.2122193872928619</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.2855771780014038</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.1317215263843536</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.1191573515534401</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.7108625173568726</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.003112657461315393</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.276156902313232</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.316151022911072</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1883,6 +2787,30 @@
       <c r="L38" t="n">
         <v>0.1572070866823196</v>
       </c>
+      <c r="M38" t="n">
+        <v>0.3458928167819977</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.12027308344841</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.1448411047458649</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.09239670634269714</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.232820749282837</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.509432077407837</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.692058324813843</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.4140140116214752</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1921,6 +2849,30 @@
       <c r="L39" t="n">
         <v>0.3652591958642006</v>
       </c>
+      <c r="M39" t="n">
+        <v>0.2795483767986298</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.1901333928108215</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.1591671705245972</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.09338555485010147</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1714625954627991</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.03155339136719704</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.785057544708252</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.019922971725464</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1959,6 +2911,30 @@
       <c r="L40" t="n">
         <v>0.1697735950350761</v>
       </c>
+      <c r="M40" t="n">
+        <v>0.2890458405017853</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1276929974555969</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.1267119497060776</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.09430520981550217</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.06295895576477051</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.168912336230278</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.533918857574463</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.375986933708191</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1997,6 +2973,30 @@
       <c r="L41" t="n">
         <v>0.14700311034685</v>
       </c>
+      <c r="M41" t="n">
+        <v>0.6226652860641479</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.1502119898796082</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.1425089091062546</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.104804091155529</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.241589069366455</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.9585428237915039</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.088143587112427</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.8126538991928101</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2035,6 +3035,30 @@
       <c r="L42" t="n">
         <v>0.4350100010633469</v>
       </c>
+      <c r="M42" t="n">
+        <v>0.3034179210662842</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.1432061195373535</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.1354586482048035</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.1086727604269981</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.270227074623108</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.8575005531311035</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.45907735824585</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.199884653091431</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2073,6 +3097,30 @@
       <c r="L43" t="n">
         <v>0.2566038613207638</v>
       </c>
+      <c r="M43" t="n">
+        <v>0.3533197641372681</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.1416634321212769</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.1250350624322891</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.1356956958770752</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.0130196250975132</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.645066261291504</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.922953605651855</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.613287627696991</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2111,6 +3159,30 @@
       <c r="L44" t="n">
         <v>0.09179548174142838</v>
       </c>
+      <c r="M44" t="n">
+        <v>0.3872150778770447</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.1482554972171783</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.1504566669464111</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.13037970662117</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.08934143930673599</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.3052590191364288</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4.046146392822266</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.211822986602783</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2149,6 +3221,30 @@
       <c r="L45" t="n">
         <v>0.1526233322918415</v>
       </c>
+      <c r="M45" t="n">
+        <v>1.660989284515381</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.1540279984474182</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.1525044739246368</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.1127839535474777</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6.796996593475342</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.907346813823096e-06</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.342833280563354</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.09798526763916</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2187,6 +3283,30 @@
       <c r="L46" t="n">
         <v>0.2495307236909866</v>
       </c>
+      <c r="M46" t="n">
+        <v>0.4371519088745117</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.1380048096179962</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.2929102778434753</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.09253634512424469</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.02611807361245155</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.0003822311409749091</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.808388233184814</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.05344443023204803</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2225,6 +3345,30 @@
       <c r="L47" t="n">
         <v>0.0443476740270853</v>
       </c>
+      <c r="M47" t="n">
+        <v>0.6351286172866821</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.3153579235076904</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.1293569207191467</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.09106260538101196</v>
+      </c>
+      <c r="Q47" t="n">
+        <v/>
+      </c>
+      <c r="R47" t="n">
+        <v/>
+      </c>
+      <c r="S47" t="n">
+        <v>3.663042306900024</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.5736672282218933</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2263,6 +3407,30 @@
       <c r="L48" t="n">
         <v>0.2815880049951375</v>
       </c>
+      <c r="M48" t="n">
+        <v>0.2388902455568314</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.1848450899124146</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.1393029689788818</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.09131518006324768</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.61382269859314</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.00522278668358922</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.145598888397217</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.155622363090515</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2301,6 +3469,30 @@
       <c r="L49" t="n">
         <v>0.1567580923438072</v>
       </c>
+      <c r="M49" t="n">
+        <v>0.2033454477787018</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.1143660098314285</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.1296913921833038</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.1007993295788765</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.1579990088939667</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.0004258441040292382</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.718151807785034</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.276211023330688</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2339,6 +3531,30 @@
       <c r="L50" t="n">
         <v>0.07593462455552072</v>
       </c>
+      <c r="M50" t="n">
+        <v>0.2344331592321396</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.1631818860769272</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.1413975954055786</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.101511187851429</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.003732240526005626</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.509374141693115</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.640293836593628</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.4774236083030701</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2377,6 +3593,30 @@
       <c r="L51" t="n">
         <v>0.2778644043952226</v>
       </c>
+      <c r="M51" t="n">
+        <v>0.1568007916212082</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.1071047633886337</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.1184171512722969</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.09416197240352631</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.709661722183228</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.01016401778906584</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.647422313690186</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.403499007225037</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2415,6 +3655,30 @@
       <c r="L52" t="n">
         <v>0.05869029648602009</v>
       </c>
+      <c r="M52" t="n">
+        <v>0.180308997631073</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.1509527713060379</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.166379913687706</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.09380128234624863</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.005886529572308064</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.3831308782100677</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.9797775745391846</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.430495023727417</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2453,6 +3717,30 @@
       <c r="L53" t="n">
         <v>0.2749384958297014</v>
       </c>
+      <c r="M53" t="n">
+        <v>0.4007555544376373</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.1090007871389389</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.1307439208030701</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.1057584062218666</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.01242714840918779</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.005363534670323133</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.151180744171143</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.9692806005477905</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2491,6 +3779,30 @@
       <c r="L54" t="n">
         <v>0.2941437385976314</v>
       </c>
+      <c r="M54" t="n">
+        <v>0.2966398894786835</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.1418803930282593</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.1235431954264641</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.09739392250776291</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.3769762217998505</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.9920254945755005</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.519714117050171</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.5750486850738525</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2529,6 +3841,30 @@
       <c r="L55" t="n">
         <v>0.2412037570029497</v>
       </c>
+      <c r="M55" t="n">
+        <v>0.2999784052371979</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.1380691230297089</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.1216242611408234</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.09445478767156601</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.1364961117506027</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.03558990359306335</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.6612358689308167</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.8107805848121643</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2567,6 +3903,30 @@
       <c r="L56" t="n">
         <v>0.1371936589479446</v>
       </c>
+      <c r="M56" t="n">
+        <v>0.2874640822410583</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.3023211061954498</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.1121779233217239</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.1076678708195686</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.21703839302063</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.009284932166337967</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.486871719360352</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.288626551628113</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2605,6 +3965,30 @@
       <c r="L57" t="n">
         <v>0.3542557448148728</v>
       </c>
+      <c r="M57" t="n">
+        <v>0.208097517490387</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.1341637223958969</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.1662720739841461</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.1018567532300949</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.873599767684937</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.04790059104561806</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.354616045951843</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.397288203239441</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2643,6 +4027,30 @@
       <c r="L58" t="n">
         <v>0.1136447597295046</v>
       </c>
+      <c r="M58" t="n">
+        <v>0.5782169699668884</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.9725493192672729</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.1207892596721649</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.1056461110711098</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.9605931043624878</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.008506406098604202</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.869241833686829</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.7302383184432983</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2681,6 +4089,30 @@
       <c r="L59" t="n">
         <v>0.01977012194693089</v>
       </c>
+      <c r="M59" t="n">
+        <v>0.2281086593866348</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.1489696204662323</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.1784958690404892</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.1249385252594948</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.099385261535645</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.7663357257843018</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.107008337974548</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.9656314849853516</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2719,6 +4151,30 @@
       <c r="L60" t="n">
         <v>0.5916934669017792</v>
       </c>
+      <c r="M60" t="n">
+        <v>0.1877071112394333</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.1003258004784584</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.121835470199585</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.08865693956613541</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.6702132821083069</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.420586109161377</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1.449351191520691</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.4939221739768982</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2757,6 +4213,30 @@
       <c r="L61" t="n">
         <v>0.08671481758356095</v>
       </c>
+      <c r="M61" t="n">
+        <v>0.3634801506996155</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.1016617268323898</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.1828965544700623</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.1084341704845428</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.516783237457275</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.5175767540931702</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1.523284912109375</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.636757493019104</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2795,6 +4275,30 @@
       <c r="L62" t="n">
         <v>0.1034850865602493</v>
       </c>
+      <c r="M62" t="n">
+        <v>0.3004795610904694</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.2031628787517548</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.1051342785358429</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.09328393638134003</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.1112788245081902</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.6725485920906067</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1.444258451461792</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.460655093193054</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2833,6 +4337,30 @@
       <c r="L63" t="n">
         <v>0.3072557721287012</v>
       </c>
+      <c r="M63" t="n">
+        <v>0.243212029337883</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.1198319718241692</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.1127517074346542</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.08830197155475616</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.0937621220946312</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.4997768402099609</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1.435244202613831</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.923504829406738</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2871,6 +4399,30 @@
       <c r="L64" t="n">
         <v>0.0650831600651145</v>
       </c>
+      <c r="M64" t="n">
+        <v>0.2809590995311737</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.3276178240776062</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.1183172836899757</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.0890011340379715</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.000209678037208505</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.752358366502449e-05</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1.349742531776428</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.04428264126181602</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2909,6 +4461,30 @@
       <c r="L65" t="n">
         <v>0.09671415984630585</v>
       </c>
+      <c r="M65" t="n">
+        <v>0.2211818993091583</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.1522942632436752</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.1180027350783348</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.092283695936203</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.3696368634700775</v>
+      </c>
+      <c r="R65" t="n">
+        <v>5.572742520598695e-05</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.2833081185817719</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.7460787296295166</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2947,6 +4523,30 @@
       <c r="L66" t="n">
         <v>0.1206617467105389</v>
       </c>
+      <c r="M66" t="n">
+        <v>0.2849556505680084</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.1360347270965576</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.1115880683064461</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.09219583868980408</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.2185154408216476</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.003048953367397189</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.907705664634705</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.925842046737671</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2985,6 +4585,30 @@
       <c r="L67" t="n">
         <v>0.1934071980416775</v>
       </c>
+      <c r="M67" t="n">
+        <v>0.2909291684627533</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.15730020403862</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.1298034638166428</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.08771666884422302</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.07151459157466888</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.2664647996425629</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1.880463123321533</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.7275111079216003</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3023,6 +4647,30 @@
       <c r="L68" t="n">
         <v>0.116908257547766</v>
       </c>
+      <c r="M68" t="n">
+        <v>0.1981856822967529</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.1694749891757965</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.1428258419036865</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.1115118935704231</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.1186193376779556</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.1697143316268921</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.412100553512573</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.7733628749847412</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3061,6 +4709,30 @@
       <c r="L69" t="n">
         <v>0.1014153368771076</v>
       </c>
+      <c r="M69" t="n">
+        <v>0.2633641362190247</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.1475455760955811</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.1082641780376434</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.07939565926790237</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.01631027646362782</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.1282260715961456</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1.985113739967346</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.202963590621948</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3099,6 +4771,30 @@
       <c r="L70" t="n">
         <v>0.1503618004731834</v>
       </c>
+      <c r="M70" t="n">
+        <v>0.2392860054969788</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.1500455290079117</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.117272675037384</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.1182647570967674</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.003257565898820758</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.0001846381492214277</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1.155661582946777</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.7912582159042358</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3136,6 +4832,30 @@
       </c>
       <c r="L71" t="n">
         <v>0.09889610148966313</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.4213149845600128</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.229131817817688</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.1095523163676262</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.09069791436195374</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1.16260039806366</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.1994333118200302</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1.639782905578613</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1.093567609786987</v>
       </c>
     </row>
     <row r="72">
